--- a/data/output/2025/evaluasi_31.xlsx
+++ b/data/output/2025/evaluasi_31.xlsx
@@ -13,6 +13,7 @@
     <sheet name="3173" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="3171" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="3172" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="3101" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -644,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -844,6 +845,454 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.626702522420858</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>43.0724090156063</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2974032891735158</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10.1098507786304</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2158150544589924</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.098738532919537</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.333947159285525</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10.49273342744036</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.6226426416545446</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q4-25_prov vs c-to-c_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-5.634574063516213</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-1.90119197175329</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-3.233430141039323</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-5.592627579907267</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-2.621021260115347</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-4.299608929048351</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3174</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-2.15873841662909</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -858,7 +1307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1058,6 +1507,202 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3175</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.01009560133869187</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3175</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8.590000000000284</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3175</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>89.18382215468472</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3175</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-17.24886650720029</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3175</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Utara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.4522683670911463</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3175</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Utara</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-22.71154173754375</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3175</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Utara</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-2.535576813127122</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1370,18 +2015,186 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>-0.9308920109037486</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3173</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Pusat</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>50.8954711217979</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3173</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Pusat</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>14.81796028800505</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3173</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Pusat</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>8.81378210227102</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3173</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Pusat</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.463894228224332</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3173</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Pusat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.53450189730276</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3173</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Pusat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>3.628688386052978</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -1398,7 +2211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1486,6 +2299,118 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3171</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2520128524295866</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3171</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>60.17746895247282</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3171</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.799019577138603</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3171</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-3.090414618864327</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1500,7 +2425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1630,20 +2555,542 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>-0.9174311926605472</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3172</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Timur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>98.31417394123856</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3172</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.326248250696784</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3172</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Timur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>18.91593181581238</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3172</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Timur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.262417575244165</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3172</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Timur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.4269536425111816</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3172</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Jakarta Timur</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>3.429378482922175</v>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3101</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.8104961026295852</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3101</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.542068127185649</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3101</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.972011042913931</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3101</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-6.206743125326717</v>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3101</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.5782759002044878</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3101</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9.346442186853814</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3101</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-6.53406404454434</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3101</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.138784940625493</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3101</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.02071046013173616</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3101</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.2443746118697941</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3101</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>9.408876414435218</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
